--- a/artfynd/A 39038-2025 artfynd.xlsx
+++ b/artfynd/A 39038-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89031721</v>
+        <v>89031453</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558145.7426151456</v>
+        <v>558146</v>
       </c>
       <c r="R2" t="n">
-        <v>6284739.167548466</v>
+        <v>6284739</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>täcker stora ytor</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,44 +790,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89031359</v>
+        <v>89031721</v>
       </c>
       <c r="B3" t="n">
-        <v>4964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558145.7426151456</v>
+        <v>558146</v>
       </c>
       <c r="R3" t="n">
-        <v>6284739.167548466</v>
+        <v>6284739</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -875,24 +862,14 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>gott om äldre och färska gnagspår i fristående aspar</t>
+          <t>täcker stora ytor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,126 +894,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89031453</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Gårdsryd, Granfallsmossen, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>558145.7426151456</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6284739.167548466</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nybro</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sankt Sigfrid</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-11-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-11-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Stefan Björn</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Stefan Björn</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39038-2025 artfynd.xlsx
+++ b/artfynd/A 39038-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89031453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89031721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>